--- a/NCAA_Seed_Test_Set2.0.xlsx
+++ b/NCAA_Seed_Test_Set2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bigoc\Documents\AU\Machine Learning\analytics_challenge\analytics_challenge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E883AA2-ED44-493C-B2D8-6111392E8888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8530A87-8CDB-42CE-A1E5-CB038E3BAFCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2091" uniqueCount="793">
   <si>
     <t>RecordID</t>
   </si>
@@ -1042,21 +1042,6 @@
     <t>Rank</t>
   </si>
   <si>
-    <t>Conf Win</t>
-  </si>
-  <si>
-    <t>Conf Loss</t>
-  </si>
-  <si>
-    <t>Non-ConferenceRecord</t>
-  </si>
-  <si>
-    <t>Road Win</t>
-  </si>
-  <si>
-    <t>Road Loss</t>
-  </si>
-  <si>
     <t>2020-21-Baylor</t>
   </si>
   <si>
@@ -2414,13 +2399,31 @@
   </si>
   <si>
     <t>2024-25-MississippiVal.</t>
+  </si>
+  <si>
+    <t>Conf W</t>
+  </si>
+  <si>
+    <t>Conf L</t>
+  </si>
+  <si>
+    <t>Non-Con W</t>
+  </si>
+  <si>
+    <t>Non-Con L</t>
+  </si>
+  <si>
+    <t>Road W</t>
+  </si>
+  <si>
+    <t>Road L</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2433,6 +2436,12 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2456,9 +2465,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2676,6 +2686,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E328377B-2F2B-4189-BD2F-1A63222F225B}">
   <dimension ref="A1:AA452"/>
   <sheetFormatPr defaultRowHeight="12.3" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="8" max="8" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.94140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
@@ -2712,54 +2726,57 @@
         <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>334</v>
+        <v>787</v>
       </c>
       <c r="M1" t="s">
-        <v>335</v>
-      </c>
-      <c r="N1" t="s">
-        <v>336</v>
-      </c>
-      <c r="P1" t="s">
-        <v>337</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>338</v>
-      </c>
-      <c r="R1" t="s">
+        <v>788</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="R1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
@@ -2842,7 +2859,7 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
@@ -2925,7 +2942,7 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
@@ -3008,7 +3025,7 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
@@ -3091,7 +3108,7 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
@@ -3174,7 +3191,7 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B7" t="s">
         <v>19</v>
@@ -3257,7 +3274,7 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B8" t="s">
         <v>19</v>
@@ -3340,7 +3357,7 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
@@ -3423,7 +3440,7 @@
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
@@ -3506,7 +3523,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
@@ -3589,7 +3606,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B12" t="s">
         <v>19</v>
@@ -3672,7 +3689,7 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B13" t="s">
         <v>19</v>
@@ -3755,7 +3772,7 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="B14" t="s">
         <v>19</v>
@@ -3838,7 +3855,7 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B15" t="s">
         <v>19</v>
@@ -3921,7 +3938,7 @@
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B16" t="s">
         <v>19</v>
@@ -4004,7 +4021,7 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="B17" t="s">
         <v>19</v>
@@ -4087,7 +4104,7 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B18" t="s">
         <v>19</v>
@@ -4170,7 +4187,7 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B19" t="s">
         <v>19</v>
@@ -4253,7 +4270,7 @@
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B20" t="s">
         <v>19</v>
@@ -4333,7 +4350,7 @@
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="B21" t="s">
         <v>19</v>
@@ -4413,7 +4430,7 @@
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B22" t="s">
         <v>19</v>
@@ -4493,7 +4510,7 @@
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B23" t="s">
         <v>19</v>
@@ -4573,7 +4590,7 @@
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B24" t="s">
         <v>19</v>
@@ -4653,7 +4670,7 @@
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B25" t="s">
         <v>19</v>
@@ -4733,7 +4750,7 @@
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="B26" t="s">
         <v>19</v>
@@ -4813,7 +4830,7 @@
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B27" t="s">
         <v>19</v>
@@ -4893,7 +4910,7 @@
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="B28" t="s">
         <v>19</v>
@@ -4973,7 +4990,7 @@
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="B29" t="s">
         <v>19</v>
@@ -5053,7 +5070,7 @@
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B30" t="s">
         <v>19</v>
@@ -5133,7 +5150,7 @@
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B31" t="s">
         <v>19</v>
@@ -5213,7 +5230,7 @@
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B32" t="s">
         <v>19</v>
@@ -5293,7 +5310,7 @@
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B33" t="s">
         <v>19</v>
@@ -5373,7 +5390,7 @@
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B34" t="s">
         <v>19</v>
@@ -5453,7 +5470,7 @@
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B35" t="s">
         <v>19</v>
@@ -5533,7 +5550,7 @@
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B36" t="s">
         <v>19</v>
@@ -5610,7 +5627,7 @@
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B37" t="s">
         <v>19</v>
@@ -5690,7 +5707,7 @@
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B38" t="s">
         <v>19</v>
@@ -5770,7 +5787,7 @@
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B39" t="s">
         <v>19</v>
@@ -5850,7 +5867,7 @@
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B40" t="s">
         <v>19</v>
@@ -5930,7 +5947,7 @@
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="B41" t="s">
         <v>19</v>
@@ -6010,7 +6027,7 @@
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="B42" t="s">
         <v>19</v>
@@ -6090,7 +6107,7 @@
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="B43" t="s">
         <v>19</v>
@@ -6170,7 +6187,7 @@
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="B44" t="s">
         <v>19</v>
@@ -6250,7 +6267,7 @@
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B45" t="s">
         <v>19</v>
@@ -6330,7 +6347,7 @@
     </row>
     <row r="46" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="B46" t="s">
         <v>19</v>
@@ -6410,7 +6427,7 @@
     </row>
     <row r="47" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="B47" t="s">
         <v>19</v>
@@ -6490,7 +6507,7 @@
     </row>
     <row r="48" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B48" t="s">
         <v>19</v>
@@ -6567,7 +6584,7 @@
     </row>
     <row r="49" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="B49" t="s">
         <v>19</v>
@@ -6647,7 +6664,7 @@
     </row>
     <row r="50" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B50" t="s">
         <v>19</v>
@@ -6724,7 +6741,7 @@
     </row>
     <row r="51" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="B51" t="s">
         <v>19</v>
@@ -6804,7 +6821,7 @@
     </row>
     <row r="52" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="B52" t="s">
         <v>19</v>
@@ -6884,7 +6901,7 @@
     </row>
     <row r="53" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B53" t="s">
         <v>19</v>
@@ -6964,13 +6981,13 @@
     </row>
     <row r="54" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="B54" t="s">
         <v>19</v>
       </c>
       <c r="C54" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="D54" t="s">
         <v>26</v>
@@ -7041,7 +7058,7 @@
     </row>
     <row r="55" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B55" t="s">
         <v>19</v>
@@ -7121,7 +7138,7 @@
     </row>
     <row r="56" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B56" t="s">
         <v>19</v>
@@ -7201,7 +7218,7 @@
     </row>
     <row r="57" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="B57" t="s">
         <v>19</v>
@@ -7281,7 +7298,7 @@
     </row>
     <row r="58" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B58" t="s">
         <v>19</v>
@@ -7361,7 +7378,7 @@
     </row>
     <row r="59" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="B59" t="s">
         <v>19</v>
@@ -7441,7 +7458,7 @@
     </row>
     <row r="60" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B60" t="s">
         <v>19</v>
@@ -7521,7 +7538,7 @@
     </row>
     <row r="61" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="B61" t="s">
         <v>19</v>
@@ -7601,7 +7618,7 @@
     </row>
     <row r="62" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B62" t="s">
         <v>19</v>
@@ -7681,7 +7698,7 @@
     </row>
     <row r="63" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B63" t="s">
         <v>19</v>
@@ -7761,7 +7778,7 @@
     </row>
     <row r="64" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="B64" t="s">
         <v>19</v>
@@ -7841,7 +7858,7 @@
     </row>
     <row r="65" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B65" t="s">
         <v>19</v>
@@ -7921,7 +7938,7 @@
     </row>
     <row r="66" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="B66" t="s">
         <v>19</v>
@@ -8001,7 +8018,7 @@
     </row>
     <row r="67" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="B67" t="s">
         <v>19</v>
@@ -8081,7 +8098,7 @@
     </row>
     <row r="68" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="B68" t="s">
         <v>19</v>
@@ -8161,7 +8178,7 @@
     </row>
     <row r="69" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="B69" t="s">
         <v>19</v>
@@ -8241,7 +8258,7 @@
     </row>
     <row r="70" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="B70" t="s">
         <v>19</v>
@@ -8321,7 +8338,7 @@
     </row>
     <row r="71" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B71" t="s">
         <v>19</v>
@@ -8401,7 +8418,7 @@
     </row>
     <row r="72" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="B72" t="s">
         <v>19</v>
@@ -8478,7 +8495,7 @@
     </row>
     <row r="73" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B73" t="s">
         <v>19</v>
@@ -8558,7 +8575,7 @@
     </row>
     <row r="74" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B74" t="s">
         <v>19</v>
@@ -8638,7 +8655,7 @@
     </row>
     <row r="75" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="B75" t="s">
         <v>19</v>
@@ -8718,7 +8735,7 @@
     </row>
     <row r="76" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="B76" t="s">
         <v>19</v>
@@ -8798,7 +8815,7 @@
     </row>
     <row r="77" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="B77" t="s">
         <v>19</v>
@@ -8878,7 +8895,7 @@
     </row>
     <row r="78" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="B78" t="s">
         <v>19</v>
@@ -8958,7 +8975,7 @@
     </row>
     <row r="79" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="B79" t="s">
         <v>19</v>
@@ -9038,7 +9055,7 @@
     </row>
     <row r="80" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B80" t="s">
         <v>19</v>
@@ -9115,7 +9132,7 @@
     </row>
     <row r="81" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="B81" t="s">
         <v>19</v>
@@ -9195,7 +9212,7 @@
     </row>
     <row r="82" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B82" t="s">
         <v>19</v>
@@ -9275,7 +9292,7 @@
     </row>
     <row r="83" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="B83" t="s">
         <v>19</v>
@@ -9355,7 +9372,7 @@
     </row>
     <row r="84" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="B84" t="s">
         <v>19</v>
@@ -9435,7 +9452,7 @@
     </row>
     <row r="85" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B85" t="s">
         <v>19</v>
@@ -9512,7 +9529,7 @@
     </row>
     <row r="86" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B86" t="s">
         <v>19</v>
@@ -9574,7 +9591,7 @@
     </row>
     <row r="87" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="B87" t="s">
         <v>19</v>
@@ -9636,7 +9653,7 @@
     </row>
     <row r="88" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="B88" t="s">
         <v>19</v>
@@ -9698,7 +9715,7 @@
     </row>
     <row r="89" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B89" t="s">
         <v>19</v>
@@ -9760,7 +9777,7 @@
     </row>
     <row r="90" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B90" t="s">
         <v>19</v>
@@ -9822,7 +9839,7 @@
     </row>
     <row r="91" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="B91" t="s">
         <v>235</v>
@@ -9905,7 +9922,7 @@
     </row>
     <row r="92" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="B92" t="s">
         <v>235</v>
@@ -9988,7 +10005,7 @@
     </row>
     <row r="93" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="B93" t="s">
         <v>235</v>
@@ -10071,7 +10088,7 @@
     </row>
     <row r="94" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="B94" t="s">
         <v>235</v>
@@ -10154,7 +10171,7 @@
     </row>
     <row r="95" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="B95" t="s">
         <v>235</v>
@@ -10237,7 +10254,7 @@
     </row>
     <row r="96" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="B96" t="s">
         <v>235</v>
@@ -10320,7 +10337,7 @@
     </row>
     <row r="97" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="B97" t="s">
         <v>235</v>
@@ -10403,7 +10420,7 @@
     </row>
     <row r="98" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="B98" t="s">
         <v>235</v>
@@ -10486,7 +10503,7 @@
     </row>
     <row r="99" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="B99" t="s">
         <v>235</v>
@@ -10569,7 +10586,7 @@
     </row>
     <row r="100" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="B100" t="s">
         <v>235</v>
@@ -10652,7 +10669,7 @@
     </row>
     <row r="101" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B101" t="s">
         <v>235</v>
@@ -10735,7 +10752,7 @@
     </row>
     <row r="102" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="B102" t="s">
         <v>235</v>
@@ -10815,7 +10832,7 @@
     </row>
     <row r="103" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B103" t="s">
         <v>235</v>
@@ -10898,7 +10915,7 @@
     </row>
     <row r="104" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="B104" t="s">
         <v>235</v>
@@ -10978,7 +10995,7 @@
     </row>
     <row r="105" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="B105" t="s">
         <v>235</v>
@@ -11061,7 +11078,7 @@
     </row>
     <row r="106" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B106" t="s">
         <v>235</v>
@@ -11141,7 +11158,7 @@
     </row>
     <row r="107" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="B107" t="s">
         <v>235</v>
@@ -11224,7 +11241,7 @@
     </row>
     <row r="108" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="B108" t="s">
         <v>235</v>
@@ -11307,7 +11324,7 @@
     </row>
     <row r="109" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="B109" t="s">
         <v>235</v>
@@ -11387,7 +11404,7 @@
     </row>
     <row r="110" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B110" t="s">
         <v>235</v>
@@ -11470,7 +11487,7 @@
     </row>
     <row r="111" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="B111" t="s">
         <v>235</v>
@@ -11550,7 +11567,7 @@
     </row>
     <row r="112" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B112" t="s">
         <v>235</v>
@@ -11630,7 +11647,7 @@
     </row>
     <row r="113" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="B113" t="s">
         <v>235</v>
@@ -11710,7 +11727,7 @@
     </row>
     <row r="114" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="B114" t="s">
         <v>235</v>
@@ -11790,7 +11807,7 @@
     </row>
     <row r="115" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="B115" t="s">
         <v>235</v>
@@ -11870,7 +11887,7 @@
     </row>
     <row r="116" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="B116" t="s">
         <v>235</v>
@@ -11950,7 +11967,7 @@
     </row>
     <row r="117" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="B117" t="s">
         <v>235</v>
@@ -12030,7 +12047,7 @@
     </row>
     <row r="118" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="B118" t="s">
         <v>235</v>
@@ -12110,7 +12127,7 @@
     </row>
     <row r="119" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="B119" t="s">
         <v>235</v>
@@ -12190,7 +12207,7 @@
     </row>
     <row r="120" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="B120" t="s">
         <v>235</v>
@@ -12270,7 +12287,7 @@
     </row>
     <row r="121" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="B121" t="s">
         <v>235</v>
@@ -12350,7 +12367,7 @@
     </row>
     <row r="122" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="B122" t="s">
         <v>235</v>
@@ -12430,7 +12447,7 @@
     </row>
     <row r="123" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="B123" t="s">
         <v>235</v>
@@ -12510,7 +12527,7 @@
     </row>
     <row r="124" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="B124" t="s">
         <v>235</v>
@@ -12590,7 +12607,7 @@
     </row>
     <row r="125" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="B125" t="s">
         <v>235</v>
@@ -12670,7 +12687,7 @@
     </row>
     <row r="126" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="B126" t="s">
         <v>235</v>
@@ -12750,7 +12767,7 @@
     </row>
     <row r="127" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B127" t="s">
         <v>235</v>
@@ -12830,7 +12847,7 @@
     </row>
     <row r="128" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="B128" t="s">
         <v>235</v>
@@ -12910,7 +12927,7 @@
     </row>
     <row r="129" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="B129" t="s">
         <v>235</v>
@@ -12990,7 +13007,7 @@
     </row>
     <row r="130" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="B130" t="s">
         <v>235</v>
@@ -13070,7 +13087,7 @@
     </row>
     <row r="131" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="B131" t="s">
         <v>235</v>
@@ -13150,7 +13167,7 @@
     </row>
     <row r="132" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="B132" t="s">
         <v>235</v>
@@ -13230,7 +13247,7 @@
     </row>
     <row r="133" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="B133" t="s">
         <v>235</v>
@@ -13310,7 +13327,7 @@
     </row>
     <row r="134" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="B134" t="s">
         <v>235</v>
@@ -13390,7 +13407,7 @@
     </row>
     <row r="135" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A135" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="B135" t="s">
         <v>235</v>
@@ -13470,7 +13487,7 @@
     </row>
     <row r="136" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="B136" t="s">
         <v>235</v>
@@ -13553,7 +13570,7 @@
     </row>
     <row r="137" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="B137" t="s">
         <v>235</v>
@@ -13633,7 +13650,7 @@
     </row>
     <row r="138" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A138" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="B138" t="s">
         <v>235</v>
@@ -13713,7 +13730,7 @@
     </row>
     <row r="139" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="B139" t="s">
         <v>235</v>
@@ -13793,7 +13810,7 @@
     </row>
     <row r="140" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A140" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="B140" t="s">
         <v>235</v>
@@ -13873,7 +13890,7 @@
     </row>
     <row r="141" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A141" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="B141" t="s">
         <v>235</v>
@@ -13953,7 +13970,7 @@
     </row>
     <row r="142" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A142" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B142" t="s">
         <v>235</v>
@@ -14033,7 +14050,7 @@
     </row>
     <row r="143" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="B143" t="s">
         <v>235</v>
@@ -14113,7 +14130,7 @@
     </row>
     <row r="144" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="B144" t="s">
         <v>235</v>
@@ -14193,7 +14210,7 @@
     </row>
     <row r="145" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="B145" t="s">
         <v>235</v>
@@ -14273,7 +14290,7 @@
     </row>
     <row r="146" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A146" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="B146" t="s">
         <v>235</v>
@@ -14353,7 +14370,7 @@
     </row>
     <row r="147" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="B147" t="s">
         <v>235</v>
@@ -14433,7 +14450,7 @@
     </row>
     <row r="148" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="B148" t="s">
         <v>235</v>
@@ -14513,13 +14530,13 @@
     </row>
     <row r="149" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A149" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="B149" t="s">
         <v>235</v>
       </c>
       <c r="C149" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="D149" t="s">
         <v>26</v>
@@ -14593,7 +14610,7 @@
     </row>
     <row r="150" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="B150" t="s">
         <v>235</v>
@@ -14673,7 +14690,7 @@
     </row>
     <row r="151" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B151" t="s">
         <v>235</v>
@@ -14753,7 +14770,7 @@
     </row>
     <row r="152" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A152" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="B152" t="s">
         <v>235</v>
@@ -14833,7 +14850,7 @@
     </row>
     <row r="153" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="B153" t="s">
         <v>235</v>
@@ -14913,7 +14930,7 @@
     </row>
     <row r="154" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="B154" t="s">
         <v>235</v>
@@ -14993,7 +15010,7 @@
     </row>
     <row r="155" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A155" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="B155" t="s">
         <v>235</v>
@@ -15073,7 +15090,7 @@
     </row>
     <row r="156" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A156" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="B156" t="s">
         <v>235</v>
@@ -15153,7 +15170,7 @@
     </row>
     <row r="157" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A157" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="B157" t="s">
         <v>235</v>
@@ -15233,7 +15250,7 @@
     </row>
     <row r="158" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A158" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="B158" t="s">
         <v>235</v>
@@ -15313,7 +15330,7 @@
     </row>
     <row r="159" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A159" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="B159" t="s">
         <v>235</v>
@@ -15393,7 +15410,7 @@
     </row>
     <row r="160" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A160" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="B160" t="s">
         <v>235</v>
@@ -15473,7 +15490,7 @@
     </row>
     <row r="161" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="B161" t="s">
         <v>235</v>
@@ -15553,7 +15570,7 @@
     </row>
     <row r="162" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A162" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="B162" t="s">
         <v>235</v>
@@ -15633,7 +15650,7 @@
     </row>
     <row r="163" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A163" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B163" t="s">
         <v>235</v>
@@ -15713,7 +15730,7 @@
     </row>
     <row r="164" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A164" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="B164" t="s">
         <v>235</v>
@@ -15793,7 +15810,7 @@
     </row>
     <row r="165" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A165" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="B165" t="s">
         <v>235</v>
@@ -15873,7 +15890,7 @@
     </row>
     <row r="166" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A166" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="B166" t="s">
         <v>235</v>
@@ -15953,7 +15970,7 @@
     </row>
     <row r="167" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A167" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="B167" t="s">
         <v>235</v>
@@ -16033,7 +16050,7 @@
     </row>
     <row r="168" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A168" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="B168" t="s">
         <v>235</v>
@@ -16113,7 +16130,7 @@
     </row>
     <row r="169" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A169" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="B169" t="s">
         <v>235</v>
@@ -16193,7 +16210,7 @@
     </row>
     <row r="170" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A170" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="B170" t="s">
         <v>235</v>
@@ -16273,7 +16290,7 @@
     </row>
     <row r="171" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A171" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="B171" t="s">
         <v>235</v>
@@ -16353,7 +16370,7 @@
     </row>
     <row r="172" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A172" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="B172" t="s">
         <v>235</v>
@@ -16433,7 +16450,7 @@
     </row>
     <row r="173" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A173" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="B173" t="s">
         <v>235</v>
@@ -16513,7 +16530,7 @@
     </row>
     <row r="174" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A174" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="B174" t="s">
         <v>235</v>
@@ -16593,7 +16610,7 @@
     </row>
     <row r="175" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A175" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="B175" t="s">
         <v>235</v>
@@ -16673,7 +16690,7 @@
     </row>
     <row r="176" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A176" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="B176" t="s">
         <v>235</v>
@@ -16753,7 +16770,7 @@
     </row>
     <row r="177" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A177" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="B177" t="s">
         <v>235</v>
@@ -16833,7 +16850,7 @@
     </row>
     <row r="178" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A178" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="B178" t="s">
         <v>235</v>
@@ -16913,7 +16930,7 @@
     </row>
     <row r="179" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A179" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="B179" t="s">
         <v>235</v>
@@ -16993,7 +17010,7 @@
     </row>
     <row r="180" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A180" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="B180" t="s">
         <v>235</v>
@@ -17073,7 +17090,7 @@
     </row>
     <row r="181" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A181" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="B181" t="s">
         <v>298</v>
@@ -17156,7 +17173,7 @@
     </row>
     <row r="182" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A182" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="B182" t="s">
         <v>298</v>
@@ -17239,7 +17256,7 @@
     </row>
     <row r="183" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A183" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="B183" t="s">
         <v>298</v>
@@ -17322,7 +17339,7 @@
     </row>
     <row r="184" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A184" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="B184" t="s">
         <v>298</v>
@@ -17405,7 +17422,7 @@
     </row>
     <row r="185" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A185" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="B185" t="s">
         <v>298</v>
@@ -17488,7 +17505,7 @@
     </row>
     <row r="186" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A186" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="B186" t="s">
         <v>298</v>
@@ -17571,7 +17588,7 @@
     </row>
     <row r="187" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A187" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="B187" t="s">
         <v>298</v>
@@ -17654,7 +17671,7 @@
     </row>
     <row r="188" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A188" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="B188" t="s">
         <v>298</v>
@@ -17737,7 +17754,7 @@
     </row>
     <row r="189" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A189" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="B189" t="s">
         <v>298</v>
@@ -17817,7 +17834,7 @@
     </row>
     <row r="190" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A190" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="B190" t="s">
         <v>298</v>
@@ -17900,7 +17917,7 @@
     </row>
     <row r="191" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A191" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B191" t="s">
         <v>298</v>
@@ -17983,7 +18000,7 @@
     </row>
     <row r="192" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A192" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="B192" t="s">
         <v>298</v>
@@ -18066,7 +18083,7 @@
     </row>
     <row r="193" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A193" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="B193" t="s">
         <v>298</v>
@@ -18149,7 +18166,7 @@
     </row>
     <row r="194" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A194" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="B194" t="s">
         <v>298</v>
@@ -18229,7 +18246,7 @@
     </row>
     <row r="195" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A195" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="B195" t="s">
         <v>298</v>
@@ -18312,7 +18329,7 @@
     </row>
     <row r="196" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A196" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="B196" t="s">
         <v>298</v>
@@ -18395,7 +18412,7 @@
     </row>
     <row r="197" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A197" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="B197" t="s">
         <v>298</v>
@@ -18475,7 +18492,7 @@
     </row>
     <row r="198" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A198" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="B198" t="s">
         <v>298</v>
@@ -18555,7 +18572,7 @@
     </row>
     <row r="199" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A199" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="B199" t="s">
         <v>298</v>
@@ -18635,7 +18652,7 @@
     </row>
     <row r="200" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A200" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="B200" t="s">
         <v>298</v>
@@ -18715,7 +18732,7 @@
     </row>
     <row r="201" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A201" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="B201" t="s">
         <v>298</v>
@@ -18798,7 +18815,7 @@
     </row>
     <row r="202" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A202" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="B202" t="s">
         <v>298</v>
@@ -18881,7 +18898,7 @@
     </row>
     <row r="203" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A203" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="B203" t="s">
         <v>298</v>
@@ -18961,7 +18978,7 @@
     </row>
     <row r="204" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A204" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="B204" t="s">
         <v>298</v>
@@ -19044,7 +19061,7 @@
     </row>
     <row r="205" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A205" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="B205" t="s">
         <v>298</v>
@@ -19127,7 +19144,7 @@
     </row>
     <row r="206" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A206" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="B206" t="s">
         <v>298</v>
@@ -19207,7 +19224,7 @@
     </row>
     <row r="207" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A207" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="B207" t="s">
         <v>298</v>
@@ -19287,7 +19304,7 @@
     </row>
     <row r="208" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A208" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="B208" t="s">
         <v>298</v>
@@ -19367,7 +19384,7 @@
     </row>
     <row r="209" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A209" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="B209" t="s">
         <v>298</v>
@@ -19447,7 +19464,7 @@
     </row>
     <row r="210" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A210" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="B210" t="s">
         <v>298</v>
@@ -19527,7 +19544,7 @@
     </row>
     <row r="211" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A211" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="B211" t="s">
         <v>298</v>
@@ -19607,7 +19624,7 @@
     </row>
     <row r="212" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A212" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="B212" t="s">
         <v>298</v>
@@ -19687,7 +19704,7 @@
     </row>
     <row r="213" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A213" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="B213" t="s">
         <v>298</v>
@@ -19767,7 +19784,7 @@
     </row>
     <row r="214" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A214" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="B214" t="s">
         <v>298</v>
@@ -19847,7 +19864,7 @@
     </row>
     <row r="215" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A215" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="B215" t="s">
         <v>298</v>
@@ -19927,7 +19944,7 @@
     </row>
     <row r="216" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A216" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="B216" t="s">
         <v>298</v>
@@ -20007,7 +20024,7 @@
     </row>
     <row r="217" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A217" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="B217" t="s">
         <v>298</v>
@@ -20087,7 +20104,7 @@
     </row>
     <row r="218" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A218" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="B218" t="s">
         <v>298</v>
@@ -20167,7 +20184,7 @@
     </row>
     <row r="219" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A219" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="B219" t="s">
         <v>298</v>
@@ -20247,7 +20264,7 @@
     </row>
     <row r="220" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A220" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="B220" t="s">
         <v>298</v>
@@ -20327,7 +20344,7 @@
     </row>
     <row r="221" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A221" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="B221" t="s">
         <v>298</v>
@@ -20407,7 +20424,7 @@
     </row>
     <row r="222" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A222" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="B222" t="s">
         <v>298</v>
@@ -20490,7 +20507,7 @@
     </row>
     <row r="223" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A223" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="B223" t="s">
         <v>298</v>
@@ -20570,7 +20587,7 @@
     </row>
     <row r="224" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A224" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="B224" t="s">
         <v>298</v>
@@ -20650,7 +20667,7 @@
     </row>
     <row r="225" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A225" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="B225" t="s">
         <v>298</v>
@@ -20730,7 +20747,7 @@
     </row>
     <row r="226" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A226" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="B226" t="s">
         <v>298</v>
@@ -20810,7 +20827,7 @@
     </row>
     <row r="227" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A227" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="B227" t="s">
         <v>298</v>
@@ -20890,7 +20907,7 @@
     </row>
     <row r="228" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A228" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="B228" t="s">
         <v>298</v>
@@ -20970,7 +20987,7 @@
     </row>
     <row r="229" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A229" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="B229" t="s">
         <v>298</v>
@@ -21050,7 +21067,7 @@
     </row>
     <row r="230" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A230" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="B230" t="s">
         <v>298</v>
@@ -21130,7 +21147,7 @@
     </row>
     <row r="231" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A231" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="B231" t="s">
         <v>298</v>
@@ -21210,7 +21227,7 @@
     </row>
     <row r="232" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A232" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="B232" t="s">
         <v>298</v>
@@ -21290,7 +21307,7 @@
     </row>
     <row r="233" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A233" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="B233" t="s">
         <v>298</v>
@@ -21370,7 +21387,7 @@
     </row>
     <row r="234" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A234" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="B234" t="s">
         <v>298</v>
@@ -21450,7 +21467,7 @@
     </row>
     <row r="235" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A235" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="B235" t="s">
         <v>298</v>
@@ -21530,7 +21547,7 @@
     </row>
     <row r="236" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A236" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="B236" t="s">
         <v>298</v>
@@ -21610,7 +21627,7 @@
     </row>
     <row r="237" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A237" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="B237" t="s">
         <v>298</v>
@@ -21690,7 +21707,7 @@
     </row>
     <row r="238" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A238" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="B238" t="s">
         <v>298</v>
@@ -21773,7 +21790,7 @@
     </row>
     <row r="239" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A239" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="B239" t="s">
         <v>298</v>
@@ -21853,7 +21870,7 @@
     </row>
     <row r="240" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A240" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="B240" t="s">
         <v>298</v>
@@ -21933,7 +21950,7 @@
     </row>
     <row r="241" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A241" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="B241" t="s">
         <v>298</v>
@@ -22013,7 +22030,7 @@
     </row>
     <row r="242" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A242" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="B242" t="s">
         <v>298</v>
@@ -22093,7 +22110,7 @@
     </row>
     <row r="243" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A243" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="B243" t="s">
         <v>298</v>
@@ -22173,7 +22190,7 @@
     </row>
     <row r="244" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A244" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="B244" t="s">
         <v>298</v>
@@ -22253,7 +22270,7 @@
     </row>
     <row r="245" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A245" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="B245" t="s">
         <v>298</v>
@@ -22333,7 +22350,7 @@
     </row>
     <row r="246" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A246" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="B246" t="s">
         <v>298</v>
@@ -22413,7 +22430,7 @@
     </row>
     <row r="247" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A247" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="B247" t="s">
         <v>298</v>
@@ -22493,7 +22510,7 @@
     </row>
     <row r="248" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A248" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="B248" t="s">
         <v>298</v>
@@ -22573,7 +22590,7 @@
     </row>
     <row r="249" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A249" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="B249" t="s">
         <v>298</v>
@@ -22653,7 +22670,7 @@
     </row>
     <row r="250" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A250" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="B250" t="s">
         <v>298</v>
@@ -22733,7 +22750,7 @@
     </row>
     <row r="251" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A251" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="B251" t="s">
         <v>298</v>
@@ -22813,7 +22830,7 @@
     </row>
     <row r="252" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A252" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="B252" t="s">
         <v>298</v>
@@ -22896,7 +22913,7 @@
     </row>
     <row r="253" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A253" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="B253" t="s">
         <v>298</v>
@@ -22976,7 +22993,7 @@
     </row>
     <row r="254" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A254" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B254" t="s">
         <v>298</v>
@@ -23056,7 +23073,7 @@
     </row>
     <row r="255" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A255" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="B255" t="s">
         <v>298</v>
@@ -23136,7 +23153,7 @@
     </row>
     <row r="256" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A256" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="B256" t="s">
         <v>298</v>
@@ -23216,7 +23233,7 @@
     </row>
     <row r="257" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A257" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="B257" t="s">
         <v>298</v>
@@ -23296,7 +23313,7 @@
     </row>
     <row r="258" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A258" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="B258" t="s">
         <v>298</v>
@@ -23376,7 +23393,7 @@
     </row>
     <row r="259" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A259" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="B259" t="s">
         <v>298</v>
@@ -23456,7 +23473,7 @@
     </row>
     <row r="260" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A260" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="B260" t="s">
         <v>298</v>
@@ -23536,7 +23553,7 @@
     </row>
     <row r="261" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A261" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="B261" t="s">
         <v>298</v>
@@ -23616,7 +23633,7 @@
     </row>
     <row r="262" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A262" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="B262" t="s">
         <v>298</v>
@@ -23696,7 +23713,7 @@
     </row>
     <row r="263" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A263" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="B263" t="s">
         <v>298</v>
@@ -23776,7 +23793,7 @@
     </row>
     <row r="264" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A264" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="B264" t="s">
         <v>298</v>
@@ -23856,7 +23873,7 @@
     </row>
     <row r="265" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A265" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="B265" t="s">
         <v>298</v>
@@ -23936,7 +23953,7 @@
     </row>
     <row r="266" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A266" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="B266" t="s">
         <v>298</v>
@@ -24016,7 +24033,7 @@
     </row>
     <row r="267" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A267" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="B267" t="s">
         <v>298</v>
@@ -24096,7 +24113,7 @@
     </row>
     <row r="268" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A268" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="B268" t="s">
         <v>298</v>
@@ -24176,7 +24193,7 @@
     </row>
     <row r="269" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A269" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="B269" t="s">
         <v>298</v>
@@ -24256,13 +24273,13 @@
     </row>
     <row r="270" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A270" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="B270" t="s">
         <v>298</v>
       </c>
       <c r="C270" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="D270" t="s">
         <v>26</v>
@@ -24336,7 +24353,7 @@
     </row>
     <row r="271" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A271" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="B271" t="s">
         <v>298</v>
@@ -24416,13 +24433,13 @@
     </row>
     <row r="272" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A272" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="B272" t="s">
         <v>320</v>
       </c>
       <c r="C272" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="D272" t="s">
         <v>59</v>
@@ -24499,7 +24516,7 @@
     </row>
     <row r="273" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A273" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="B273" t="s">
         <v>320</v>
@@ -24582,7 +24599,7 @@
     </row>
     <row r="274" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A274" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="B274" t="s">
         <v>320</v>
@@ -24665,7 +24682,7 @@
     </row>
     <row r="275" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A275" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="B275" t="s">
         <v>320</v>
@@ -24748,7 +24765,7 @@
     </row>
     <row r="276" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A276" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="B276" t="s">
         <v>320</v>
@@ -24831,7 +24848,7 @@
     </row>
     <row r="277" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A277" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="B277" t="s">
         <v>320</v>
@@ -24914,7 +24931,7 @@
     </row>
     <row r="278" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A278" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="B278" t="s">
         <v>320</v>
@@ -24997,7 +25014,7 @@
     </row>
     <row r="279" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A279" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="B279" t="s">
         <v>320</v>
@@ -25077,7 +25094,7 @@
     </row>
     <row r="280" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A280" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="B280" t="s">
         <v>320</v>
@@ -25160,7 +25177,7 @@
     </row>
     <row r="281" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A281" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="B281" t="s">
         <v>320</v>
@@ -25240,7 +25257,7 @@
     </row>
     <row r="282" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A282" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="B282" t="s">
         <v>320</v>
@@ -25323,7 +25340,7 @@
     </row>
     <row r="283" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A283" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="B283" t="s">
         <v>320</v>
@@ -25406,7 +25423,7 @@
     </row>
     <row r="284" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A284" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="B284" t="s">
         <v>320</v>
@@ -25489,7 +25506,7 @@
     </row>
     <row r="285" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A285" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="B285" t="s">
         <v>320</v>
@@ -25572,7 +25589,7 @@
     </row>
     <row r="286" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A286" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="B286" t="s">
         <v>320</v>
@@ -25652,7 +25669,7 @@
     </row>
     <row r="287" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A287" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="B287" t="s">
         <v>320</v>
@@ -25735,7 +25752,7 @@
     </row>
     <row r="288" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A288" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="B288" t="s">
         <v>320</v>
@@ -25818,7 +25835,7 @@
     </row>
     <row r="289" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A289" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="B289" t="s">
         <v>320</v>
@@ -25898,7 +25915,7 @@
     </row>
     <row r="290" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A290" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="B290" t="s">
         <v>320</v>
@@ -25978,7 +25995,7 @@
     </row>
     <row r="291" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A291" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="B291" t="s">
         <v>320</v>
@@ -26058,7 +26075,7 @@
     </row>
     <row r="292" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A292" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="B292" t="s">
         <v>320</v>
@@ -26138,7 +26155,7 @@
     </row>
     <row r="293" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A293" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="B293" t="s">
         <v>320</v>
@@ -26218,7 +26235,7 @@
     </row>
     <row r="294" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A294" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="B294" t="s">
         <v>320</v>
@@ -26298,7 +26315,7 @@
     </row>
     <row r="295" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A295" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="B295" t="s">
         <v>320</v>
@@ -26378,7 +26395,7 @@
     </row>
     <row r="296" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A296" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="B296" t="s">
         <v>320</v>
@@ -26458,7 +26475,7 @@
     </row>
     <row r="297" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A297" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="B297" t="s">
         <v>320</v>
@@ -26541,7 +26558,7 @@
     </row>
     <row r="298" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A298" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="B298" t="s">
         <v>320</v>
@@ -26621,7 +26638,7 @@
     </row>
     <row r="299" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A299" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B299" t="s">
         <v>320</v>
@@ -26701,7 +26718,7 @@
     </row>
     <row r="300" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A300" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="B300" t="s">
         <v>320</v>
@@ -26781,7 +26798,7 @@
     </row>
     <row r="301" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A301" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="B301" t="s">
         <v>320</v>
@@ -26861,7 +26878,7 @@
     </row>
     <row r="302" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A302" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="B302" t="s">
         <v>320</v>
@@ -26944,7 +26961,7 @@
     </row>
     <row r="303" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A303" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="B303" t="s">
         <v>320</v>
@@ -27027,7 +27044,7 @@
     </row>
     <row r="304" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A304" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="B304" t="s">
         <v>320</v>
@@ -27107,7 +27124,7 @@
     </row>
     <row r="305" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A305" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="B305" t="s">
         <v>320</v>
@@ -27187,7 +27204,7 @@
     </row>
     <row r="306" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A306" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="B306" t="s">
         <v>320</v>
@@ -27267,7 +27284,7 @@
     </row>
     <row r="307" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A307" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="B307" t="s">
         <v>320</v>
@@ -27347,7 +27364,7 @@
     </row>
     <row r="308" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A308" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="B308" t="s">
         <v>320</v>
@@ -27427,7 +27444,7 @@
     </row>
     <row r="309" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A309" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="B309" t="s">
         <v>320</v>
@@ -27510,7 +27527,7 @@
     </row>
     <row r="310" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A310" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="B310" t="s">
         <v>320</v>
@@ -27590,7 +27607,7 @@
     </row>
     <row r="311" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A311" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="B311" t="s">
         <v>320</v>
@@ -27670,7 +27687,7 @@
     </row>
     <row r="312" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A312" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="B312" t="s">
         <v>320</v>
@@ -27753,7 +27770,7 @@
     </row>
     <row r="313" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A313" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="B313" t="s">
         <v>320</v>
@@ -27833,7 +27850,7 @@
     </row>
     <row r="314" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A314" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="B314" t="s">
         <v>320</v>
@@ -27916,7 +27933,7 @@
     </row>
     <row r="315" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A315" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="B315" t="s">
         <v>320</v>
@@ -27996,7 +28013,7 @@
     </row>
     <row r="316" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A316" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="B316" t="s">
         <v>320</v>
@@ -28076,7 +28093,7 @@
     </row>
     <row r="317" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A317" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="B317" t="s">
         <v>320</v>
@@ -28156,7 +28173,7 @@
     </row>
     <row r="318" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A318" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="B318" t="s">
         <v>320</v>
@@ -28236,7 +28253,7 @@
     </row>
     <row r="319" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A319" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="B319" t="s">
         <v>320</v>
@@ -28316,7 +28333,7 @@
     </row>
     <row r="320" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A320" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="B320" t="s">
         <v>320</v>
@@ -28396,7 +28413,7 @@
     </row>
     <row r="321" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A321" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="B321" t="s">
         <v>320</v>
@@ -28479,7 +28496,7 @@
     </row>
     <row r="322" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A322" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="B322" t="s">
         <v>320</v>
@@ -28559,7 +28576,7 @@
     </row>
     <row r="323" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A323" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="B323" t="s">
         <v>320</v>
@@ -28639,7 +28656,7 @@
     </row>
     <row r="324" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A324" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="B324" t="s">
         <v>320</v>
@@ -28719,7 +28736,7 @@
     </row>
     <row r="325" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A325" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="B325" t="s">
         <v>320</v>
@@ -28799,7 +28816,7 @@
     </row>
     <row r="326" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A326" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="B326" t="s">
         <v>320</v>
@@ -28879,7 +28896,7 @@
     </row>
     <row r="327" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A327" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="B327" t="s">
         <v>320</v>
@@ -28959,7 +28976,7 @@
     </row>
     <row r="328" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A328" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="B328" t="s">
         <v>320</v>
@@ -29039,7 +29056,7 @@
     </row>
     <row r="329" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A329" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="B329" t="s">
         <v>320</v>
@@ -29119,7 +29136,7 @@
     </row>
     <row r="330" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A330" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="B330" t="s">
         <v>320</v>
@@ -29199,7 +29216,7 @@
     </row>
     <row r="331" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A331" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="B331" t="s">
         <v>320</v>
@@ -29279,7 +29296,7 @@
     </row>
     <row r="332" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A332" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B332" t="s">
         <v>320</v>
@@ -29359,7 +29376,7 @@
     </row>
     <row r="333" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A333" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="B333" t="s">
         <v>320</v>
@@ -29439,7 +29456,7 @@
     </row>
     <row r="334" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A334" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="B334" t="s">
         <v>320</v>
@@ -29519,7 +29536,7 @@
     </row>
     <row r="335" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A335" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="B335" t="s">
         <v>320</v>
@@ -29599,7 +29616,7 @@
     </row>
     <row r="336" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A336" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="B336" t="s">
         <v>320</v>
@@ -29679,7 +29696,7 @@
     </row>
     <row r="337" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A337" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="B337" t="s">
         <v>320</v>
@@ -29759,7 +29776,7 @@
     </row>
     <row r="338" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A338" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="B338" t="s">
         <v>320</v>
@@ -29839,7 +29856,7 @@
     </row>
     <row r="339" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A339" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="B339" t="s">
         <v>320</v>
@@ -29919,7 +29936,7 @@
     </row>
     <row r="340" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A340" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="B340" t="s">
         <v>320</v>
@@ -29999,7 +30016,7 @@
     </row>
     <row r="341" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A341" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B341" t="s">
         <v>320</v>
@@ -30079,7 +30096,7 @@
     </row>
     <row r="342" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A342" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B342" t="s">
         <v>320</v>
@@ -30159,7 +30176,7 @@
     </row>
     <row r="343" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A343" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="B343" t="s">
         <v>320</v>
@@ -30239,7 +30256,7 @@
     </row>
     <row r="344" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A344" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="B344" t="s">
         <v>320</v>
@@ -30319,7 +30336,7 @@
     </row>
     <row r="345" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A345" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="B345" t="s">
         <v>320</v>
@@ -30399,7 +30416,7 @@
     </row>
     <row r="346" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A346" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="B346" t="s">
         <v>320</v>
@@ -30479,7 +30496,7 @@
     </row>
     <row r="347" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A347" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="B347" t="s">
         <v>320</v>
@@ -30559,7 +30576,7 @@
     </row>
     <row r="348" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A348" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="B348" t="s">
         <v>320</v>
@@ -30639,7 +30656,7 @@
     </row>
     <row r="349" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A349" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="B349" t="s">
         <v>320</v>
@@ -30719,7 +30736,7 @@
     </row>
     <row r="350" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A350" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="B350" t="s">
         <v>320</v>
@@ -30799,7 +30816,7 @@
     </row>
     <row r="351" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A351" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="B351" t="s">
         <v>320</v>
@@ -30879,7 +30896,7 @@
     </row>
     <row r="352" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A352" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="B352" t="s">
         <v>320</v>
@@ -30959,7 +30976,7 @@
     </row>
     <row r="353" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A353" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="B353" t="s">
         <v>320</v>
@@ -31039,7 +31056,7 @@
     </row>
     <row r="354" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A354" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="B354" t="s">
         <v>320</v>
@@ -31119,13 +31136,13 @@
     </row>
     <row r="355" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A355" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="B355" t="s">
         <v>320</v>
       </c>
       <c r="C355" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="D355" t="s">
         <v>26</v>
@@ -31199,7 +31216,7 @@
     </row>
     <row r="356" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A356" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="B356" t="s">
         <v>320</v>
@@ -31279,7 +31296,7 @@
     </row>
     <row r="357" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A357" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="B357" t="s">
         <v>320</v>
@@ -31359,7 +31376,7 @@
     </row>
     <row r="358" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A358" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="B358" t="s">
         <v>320</v>
@@ -31439,7 +31456,7 @@
     </row>
     <row r="359" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A359" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="B359" t="s">
         <v>320</v>
@@ -31519,7 +31536,7 @@
     </row>
     <row r="360" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A360" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="B360" t="s">
         <v>320</v>
@@ -31599,7 +31616,7 @@
     </row>
     <row r="361" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A361" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="B361" t="s">
         <v>320</v>
@@ -31679,7 +31696,7 @@
     </row>
     <row r="362" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A362" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="B362" t="s">
         <v>328</v>
@@ -31762,7 +31779,7 @@
     </row>
     <row r="363" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A363" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="B363" t="s">
         <v>328</v>
@@ -31845,7 +31862,7 @@
     </row>
     <row r="364" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A364" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="B364" t="s">
         <v>328</v>
@@ -31928,7 +31945,7 @@
     </row>
     <row r="365" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A365" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="B365" t="s">
         <v>328</v>
@@ -32011,7 +32028,7 @@
     </row>
     <row r="366" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A366" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="B366" t="s">
         <v>328</v>
@@ -32094,7 +32111,7 @@
     </row>
     <row r="367" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A367" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="B367" t="s">
         <v>328</v>
@@ -32177,7 +32194,7 @@
     </row>
     <row r="368" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A368" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="B368" t="s">
         <v>328</v>
@@ -32260,7 +32277,7 @@
     </row>
     <row r="369" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A369" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="B369" t="s">
         <v>328</v>
@@ -32340,7 +32357,7 @@
     </row>
     <row r="370" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A370" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="B370" t="s">
         <v>328</v>
@@ -32420,7 +32437,7 @@
     </row>
     <row r="371" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A371" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="B371" t="s">
         <v>328</v>
@@ -32503,7 +32520,7 @@
     </row>
     <row r="372" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A372" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="B372" t="s">
         <v>328</v>
@@ -32583,7 +32600,7 @@
     </row>
     <row r="373" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A373" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="B373" t="s">
         <v>328</v>
@@ -32663,7 +32680,7 @@
     </row>
     <row r="374" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A374" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="B374" t="s">
         <v>328</v>
@@ -32743,7 +32760,7 @@
     </row>
     <row r="375" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A375" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="B375" t="s">
         <v>328</v>
@@ -32823,7 +32840,7 @@
     </row>
     <row r="376" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A376" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="B376" t="s">
         <v>328</v>
@@ -32903,7 +32920,7 @@
     </row>
     <row r="377" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A377" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="B377" t="s">
         <v>328</v>
@@ -32983,7 +33000,7 @@
     </row>
     <row r="378" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A378" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="B378" t="s">
         <v>328</v>
@@ -33063,7 +33080,7 @@
     </row>
     <row r="379" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A379" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="B379" t="s">
         <v>328</v>
@@ -33143,7 +33160,7 @@
     </row>
     <row r="380" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A380" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="B380" t="s">
         <v>328</v>
@@ -33226,7 +33243,7 @@
     </row>
     <row r="381" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A381" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="B381" t="s">
         <v>328</v>
@@ -33306,7 +33323,7 @@
     </row>
     <row r="382" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A382" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="B382" t="s">
         <v>328</v>
@@ -33386,7 +33403,7 @@
     </row>
     <row r="383" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A383" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="B383" t="s">
         <v>328</v>
@@ -33466,7 +33483,7 @@
     </row>
     <row r="384" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A384" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="B384" t="s">
         <v>328</v>
@@ -33549,7 +33566,7 @@
     </row>
     <row r="385" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A385" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="B385" t="s">
         <v>328</v>
@@ -33629,7 +33646,7 @@
     </row>
     <row r="386" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A386" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="B386" t="s">
         <v>328</v>
@@ -33709,7 +33726,7 @@
     </row>
     <row r="387" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A387" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="B387" t="s">
         <v>328</v>
@@ -33789,7 +33806,7 @@
     </row>
     <row r="388" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A388" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="B388" t="s">
         <v>328</v>
@@ -33869,7 +33886,7 @@
     </row>
     <row r="389" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A389" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="B389" t="s">
         <v>328</v>
@@ -33949,7 +33966,7 @@
     </row>
     <row r="390" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A390" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="B390" t="s">
         <v>328</v>
@@ -34029,7 +34046,7 @@
     </row>
     <row r="391" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A391" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="B391" t="s">
         <v>328</v>
@@ -34112,7 +34129,7 @@
     </row>
     <row r="392" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A392" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="B392" t="s">
         <v>328</v>
@@ -34192,7 +34209,7 @@
     </row>
     <row r="393" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A393" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="B393" t="s">
         <v>328</v>
@@ -34272,7 +34289,7 @@
     </row>
     <row r="394" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A394" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="B394" t="s">
         <v>328</v>
@@ -34355,7 +34372,7 @@
     </row>
     <row r="395" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A395" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="B395" t="s">
         <v>328</v>
@@ -34435,7 +34452,7 @@
     </row>
     <row r="396" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A396" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="B396" t="s">
         <v>328</v>
@@ -34515,7 +34532,7 @@
     </row>
     <row r="397" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A397" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="B397" t="s">
         <v>328</v>
@@ -34595,7 +34612,7 @@
     </row>
     <row r="398" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A398" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="B398" t="s">
         <v>328</v>
@@ -34675,7 +34692,7 @@
     </row>
     <row r="399" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A399" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="B399" t="s">
         <v>328</v>
@@ -34755,7 +34772,7 @@
     </row>
     <row r="400" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A400" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="B400" t="s">
         <v>328</v>
@@ -34835,7 +34852,7 @@
     </row>
     <row r="401" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A401" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="B401" t="s">
         <v>328</v>
@@ -34915,7 +34932,7 @@
     </row>
     <row r="402" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A402" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="B402" t="s">
         <v>328</v>
@@ -34995,7 +35012,7 @@
     </row>
     <row r="403" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A403" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="B403" t="s">
         <v>328</v>
@@ -35075,7 +35092,7 @@
     </row>
     <row r="404" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A404" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="B404" t="s">
         <v>328</v>
@@ -35155,7 +35172,7 @@
     </row>
     <row r="405" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A405" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="B405" t="s">
         <v>328</v>
@@ -35235,7 +35252,7 @@
     </row>
     <row r="406" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A406" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="B406" t="s">
         <v>328</v>
@@ -35315,7 +35332,7 @@
     </row>
     <row r="407" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A407" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="B407" t="s">
         <v>328</v>
@@ -35395,7 +35412,7 @@
     </row>
     <row r="408" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A408" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="B408" t="s">
         <v>328</v>
@@ -35475,7 +35492,7 @@
     </row>
     <row r="409" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A409" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="B409" t="s">
         <v>328</v>
@@ -35555,7 +35572,7 @@
     </row>
     <row r="410" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A410" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="B410" t="s">
         <v>328</v>
@@ -35635,7 +35652,7 @@
     </row>
     <row r="411" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A411" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="B411" t="s">
         <v>328</v>
@@ -35715,7 +35732,7 @@
     </row>
     <row r="412" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A412" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="B412" t="s">
         <v>328</v>
@@ -35795,7 +35812,7 @@
     </row>
     <row r="413" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A413" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="B413" t="s">
         <v>328</v>
@@ -35875,7 +35892,7 @@
     </row>
     <row r="414" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A414" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="B414" t="s">
         <v>328</v>
@@ -35955,7 +35972,7 @@
     </row>
     <row r="415" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A415" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="B415" t="s">
         <v>328</v>
@@ -36035,7 +36052,7 @@
     </row>
     <row r="416" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A416" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="B416" t="s">
         <v>328</v>
@@ -36115,7 +36132,7 @@
     </row>
     <row r="417" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A417" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="B417" t="s">
         <v>328</v>
@@ -36198,7 +36215,7 @@
     </row>
     <row r="418" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A418" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="B418" t="s">
         <v>328</v>
@@ -36278,7 +36295,7 @@
     </row>
     <row r="419" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A419" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="B419" t="s">
         <v>328</v>
@@ -36358,7 +36375,7 @@
     </row>
     <row r="420" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A420" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="B420" t="s">
         <v>328</v>
@@ -36438,7 +36455,7 @@
     </row>
     <row r="421" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A421" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="B421" t="s">
         <v>328</v>
@@ -36518,7 +36535,7 @@
     </row>
     <row r="422" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A422" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="B422" t="s">
         <v>328</v>
@@ -36598,7 +36615,7 @@
     </row>
     <row r="423" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A423" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="B423" t="s">
         <v>328</v>
@@ -36678,7 +36695,7 @@
     </row>
     <row r="424" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A424" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="B424" t="s">
         <v>328</v>
@@ -36758,7 +36775,7 @@
     </row>
     <row r="425" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A425" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="B425" t="s">
         <v>328</v>
@@ -36838,7 +36855,7 @@
     </row>
     <row r="426" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A426" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="B426" t="s">
         <v>328</v>
@@ -36918,7 +36935,7 @@
     </row>
     <row r="427" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A427" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="B427" t="s">
         <v>328</v>
@@ -36998,7 +37015,7 @@
     </row>
     <row r="428" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A428" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="B428" t="s">
         <v>328</v>
@@ -37078,7 +37095,7 @@
     </row>
     <row r="429" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A429" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="B429" t="s">
         <v>328</v>
@@ -37158,7 +37175,7 @@
     </row>
     <row r="430" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A430" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="B430" t="s">
         <v>328</v>
@@ -37241,7 +37258,7 @@
     </row>
     <row r="431" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A431" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="B431" t="s">
         <v>328</v>
@@ -37321,13 +37338,13 @@
     </row>
     <row r="432" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A432" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="B432" t="s">
         <v>328</v>
       </c>
       <c r="C432" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="D432" t="s">
         <v>26</v>
@@ -37401,7 +37418,7 @@
     </row>
     <row r="433" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A433" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="B433" t="s">
         <v>328</v>
@@ -37481,7 +37498,7 @@
     </row>
     <row r="434" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A434" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="B434" t="s">
         <v>328</v>
@@ -37561,7 +37578,7 @@
     </row>
     <row r="435" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A435" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="B435" t="s">
         <v>328</v>
@@ -37641,7 +37658,7 @@
     </row>
     <row r="436" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A436" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="B436" t="s">
         <v>328</v>
@@ -37721,7 +37738,7 @@
     </row>
     <row r="437" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A437" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="B437" t="s">
         <v>328</v>
@@ -37801,7 +37818,7 @@
     </row>
     <row r="438" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A438" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="B438" t="s">
         <v>328</v>
@@ -37881,7 +37898,7 @@
     </row>
     <row r="439" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A439" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="B439" t="s">
         <v>328</v>
@@ -37961,7 +37978,7 @@
     </row>
     <row r="440" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A440" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B440" t="s">
         <v>328</v>
@@ -38041,7 +38058,7 @@
     </row>
     <row r="441" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A441" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="B441" t="s">
         <v>328</v>
@@ -38121,7 +38138,7 @@
     </row>
     <row r="442" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A442" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="B442" t="s">
         <v>328</v>
@@ -38201,7 +38218,7 @@
     </row>
     <row r="443" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A443" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="B443" t="s">
         <v>328</v>
@@ -38281,7 +38298,7 @@
     </row>
     <row r="444" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A444" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="B444" t="s">
         <v>328</v>
@@ -38361,7 +38378,7 @@
     </row>
     <row r="445" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A445" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="B445" t="s">
         <v>328</v>
@@ -38441,7 +38458,7 @@
     </row>
     <row r="446" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A446" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="B446" t="s">
         <v>328</v>
@@ -38521,7 +38538,7 @@
     </row>
     <row r="447" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A447" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="B447" t="s">
         <v>328</v>
@@ -38601,7 +38618,7 @@
     </row>
     <row r="448" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A448" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="B448" t="s">
         <v>328</v>
@@ -38681,7 +38698,7 @@
     </row>
     <row r="449" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A449" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B449" t="s">
         <v>328</v>
@@ -38761,7 +38778,7 @@
     </row>
     <row r="450" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A450" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="B450" t="s">
         <v>328</v>
@@ -38841,7 +38858,7 @@
     </row>
     <row r="451" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A451" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="B451" t="s">
         <v>328</v>
@@ -38921,7 +38938,7 @@
     </row>
     <row r="452" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A452" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="B452" t="s">
         <v>328</v>
